--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D2">
-        <v>269</v>
+        <v>334</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D3">
-        <v>275</v>
+        <v>361</v>
       </c>
       <c r="E3">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E2">
         <v>7</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>426</v>
